--- a/data/research/model_ledgers/kbo-tie-aware-elo.xlsx
+++ b/data/research/model_ledgers/kbo-tie-aware-elo.xlsx
@@ -1354,14 +1354,26 @@
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>-0.2758</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:57.021892Z</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -1456,14 +1468,26 @@
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>-0.2059</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:57.094406Z</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
@@ -1558,14 +1582,26 @@
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>-0.1551</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:57.167554Z</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr"/>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>

--- a/data/research/model_ledgers/kbo-tie-aware-elo.xlsx
+++ b/data/research/model_ledgers/kbo-tie-aware-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1712,8 +1712,1028 @@
       <c r="AI11" s="2" t="inlineStr"/>
       <c r="AJ11" s="2" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>0e792aa45a1a42f8</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7b7a37e6fe66623226dedb08ee198b13ca20765ee4cc1b4e5ff21f97b2e7a3ba</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>69519</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.578629</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.1584609327731092</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:37.756404Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>b52a722bc7724696</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7b7a37e6fe66623226dedb08ee198b13ca20765ee4cc1b4e5ff21f97b2e7a3ba</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69520</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.538431</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>-0.051732934426229504</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:38.592246Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>4cbb503883814f8a</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7b7a37e6fe66623226dedb08ee198b13ca20765ee4cc1b4e5ff21f97b2e7a3ba</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69521</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.539389</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.020158230769230845</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:39.719042Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>54ac688f2da645d1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7b7a37e6fe66623226dedb08ee198b13ca20765ee4cc1b4e5ff21f97b2e7a3ba</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>69522</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.578674</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>-0.04109786311787067</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:40.881700Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ffee44c83d434027</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7b7a37e6fe66623226dedb08ee198b13ca20765ee4cc1b4e5ff21f97b2e7a3ba</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69523</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.573348</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>0.08315192156862744</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:42.112636Z</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>9ab1a63faa954f70</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>69519</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0.578629</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0.1584609327731092</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:48.171174Z</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>310519ce75d94ac2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>69520</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.538431</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>-0.051732934426229504</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.042489Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>172d727798d74513</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>69521</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.539389</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0.020158230769230845</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.843883Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>418bd0519b7b498b</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>69522</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.578674</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>-0.04109786311787067</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:50.877475Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>52cd5a722ff341c7</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>69523</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.573348</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0.08315192156862744</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796672Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ11"/>
+  <autoFilter ref="A1:AJ21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/kbo-tie-aware-elo.xlsx
+++ b/data/research/model_ledgers/kbo-tie-aware-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1712,8 +1712,2108 @@
       <c r="AI11" s="2" t="inlineStr"/>
       <c r="AJ11" s="2" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>0e792aa45a1a42f8</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7b7a37e6fe66623226dedb08ee198b13ca20765ee4cc1b4e5ff21f97b2e7a3ba</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>69519</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.578629</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.1584609327731092</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:37.756404Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>b52a722bc7724696</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7b7a37e6fe66623226dedb08ee198b13ca20765ee4cc1b4e5ff21f97b2e7a3ba</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69520</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.538431</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>-0.051732934426229504</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:38.592246Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>4cbb503883814f8a</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7b7a37e6fe66623226dedb08ee198b13ca20765ee4cc1b4e5ff21f97b2e7a3ba</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69521</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.539389</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.020158230769230845</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:39.719042Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>54ac688f2da645d1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7b7a37e6fe66623226dedb08ee198b13ca20765ee4cc1b4e5ff21f97b2e7a3ba</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>69522</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.578674</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>-0.04109786311787067</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:40.881700Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ffee44c83d434027</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7b7a37e6fe66623226dedb08ee198b13ca20765ee4cc1b4e5ff21f97b2e7a3ba</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69523</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.573348</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>0.08315192156862744</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:42.112636Z</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>9ab1a63faa954f70</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>69519</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0.578629</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0.1584609327731092</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:48.171174Z</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>310519ce75d94ac2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>69520</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.538431</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>-0.051732934426229504</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.042489Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>172d727798d74513</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>69521</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.539389</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0.020158230769230845</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.843883Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>418bd0519b7b498b</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>69522</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.578674</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>-0.04109786311787067</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:50.877475Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>52cd5a722ff341c7</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>69523</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.573348</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0.08315192156862744</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796672Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>7f4054ff023749fe</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2b2a542f812870ef1364d4456bb2ec78eae2a1dc5771e02d8709a8b66348eb04</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>76203</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.528545</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>-0.001971431924882583</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:15:18.304451Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>3680c014b6d74417</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2b2a542f812870ef1364d4456bb2ec78eae2a1dc5771e02d8709a8b66348eb04</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>76204</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.541292</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>-0.008257549549549492</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:15:19.044211Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>39ca93934c254ff1</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2b2a542f812870ef1364d4456bb2ec78eae2a1dc5771e02d8709a8b66348eb04</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>76206</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.597744</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>-0.042543769784172625</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:15:19.912693Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>92f64c622f184585</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2b2a542f812870ef1364d4456bb2ec78eae2a1dc5771e02d8709a8b66348eb04</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>76207</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.531537</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.08108654954954952</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:15:20.391841Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>c7a9dd1410464ee3</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2b2a542f812870ef1364d4456bb2ec78eae2a1dc5771e02d8709a8b66348eb04</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>76208</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.575849</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.7101449275362319</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>-0.13429592753623187</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:15:21.137610Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>466bfcadf76a4024</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>76203</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.528545</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>0.028545000000000043</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:31.891013Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:25:33.149309Z</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>d43807b33bc54c15</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>76204</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.541292</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>-0.008257549549549492</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:32.786185Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>-0.0902</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:25:33.266501Z</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>c48d3b2af4994bc8</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>76206</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.597744</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>-0.05260565034965026</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:33.260921Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>-0.2890</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:25:33.380705Z</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>cb5bb2b91d7e4644</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>76207</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.531537</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.07070750691244243</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:33.722273Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0.0850</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:25:33.531966Z</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>bcce88aeede54883</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>76208</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.575849</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.7101449275362319</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>-0.13429592753623187</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:34.448940Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>-0.3699</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:25:33.649857Z</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ11"/>
+  <autoFilter ref="A1:AJ31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>